--- a/artfynd/A 26907-2026 artfynd.xlsx
+++ b/artfynd/A 26907-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83650948</v>
+        <v>83650946</v>
       </c>
       <c r="B2" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>220785</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,14 +710,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SKÖVDE 660145, Vg</t>
+          <t>SKÖVDE 660121, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>431469.3441623891</v>
+        <v>431514</v>
       </c>
       <c r="R2" t="n">
-        <v>6483957.218432217</v>
+        <v>6483907</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,7 +744,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>1891C52D-E95A-4F99-8953-D11C3EDD8ABF</t>
+          <t>0A72779C-D864-4816-A789-F619F50204F9</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -757,24 +752,14 @@
           <t>2006-05-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2006-05-10</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>{286E7291-1C51-4E78-85BC-9AAD077155F6}</t>
+          <t>{3EF949BE-ECF0-4902-968E-C4B3BEC940DA}</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>83650946</v>
+        <v>83650945</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>223246</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,14 +825,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SKÖVDE 660121, Vg</t>
+          <t>SKÖVDE 660107, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431514.033730829</v>
+        <v>431483</v>
       </c>
       <c r="R3" t="n">
-        <v>6483906.765860976</v>
+        <v>6483872</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,7 +859,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0A72779C-D864-4816-A789-F619F50204F9</t>
+          <t>98F52B09-DD33-446A-A9E4-FFF9D8F69F66</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -887,24 +867,14 @@
           <t>2006-05-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2006-05-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>{3EF949BE-ECF0-4902-968E-C4B3BEC940DA}</t>
+          <t>{C003925D-D8EE-4217-9ADD-FD0B10F746A4}</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,6 +898,121 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>83650948</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SKÖVDE 660145, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>431469</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6483957</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1891C52D-E95A-4F99-8953-D11C3EDD8ABF</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2006-05-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2006-05-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>{286E7291-1C51-4E78-85BC-9AAD077155F6}</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna Stenström, Skövde Kommun</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>

--- a/artfynd/A 26907-2026 artfynd.xlsx
+++ b/artfynd/A 26907-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83650946</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83650945</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,8 +1032,18 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83650948</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>